--- a/Mota-Mapping-Du-Lieu.xlsx
+++ b/Mota-Mapping-Du-Lieu.xlsx
@@ -9,8 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Tổng quan đầu vào" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Dữ liệu đầu ra" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Mapping chi tiết" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Bảng tra tên đơn vị" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Xử lý dữ liệu" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +19,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="005B7178"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -58,11 +63,12 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <i val="1"/>
-      <sz val="10"/>
+      <b val="1"/>
+      <color rgb="00005D69"/>
+      <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -79,6 +85,11 @@
         <fgColor rgb="00F5F7F8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF1F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -92,27 +103,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -479,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -493,403 +505,413 @@
     <col width="50" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Truy cập bằng email UEH (@ueh.edu.vn) để được cấp quyền xem các file Google Sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>File (bấm để xem)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Mô tả</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Đơn vị cung cấp</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Header row</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Sheet đầu ra</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Tình trạng</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="2" t="n">
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>01-quymo-sinhvien-dh.xlsx</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Quy mô sinh viên đại học (ĐHCQ, VLVH, CTLK)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Ban Đào tạo</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Sheet1</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Quy mô sinh viên</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Dùng</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="4" t="n">
+      <c r="I3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>02-hocphan-sotiet-2025.xlsx</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Học phần &amp; số tiết 2025</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Ban Đào tạo</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Sheet 1</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Phụ lục 2. DS môn học 2025</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Dùng</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Chưa có phân Khoa — ghép với file 03 theo Mã HP.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="2" t="n">
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>03-monhoc-khoa-phutrach.xlsx</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Mã HP → Khoa phụ trách (có tên canonical sẵn)</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Ban Đào tạo</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Sheet1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Phụ lục 2. DS môn học 2025</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Dùng</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Cũng dùng làm nguồn tên đơn vị chuẩn hoá.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="4" t="n">
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>04-ctdt-co-phankhoa.xlsx</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>CTĐT có phân Khoa (146 CT)</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Ban Bảo đảm chất lượng - Phát triển chương trình</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Chuongtrinhdaotao</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Chuongtrinhdaotao</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Dùng</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>Mã CT khác với của Sau Đại học. Khoa/Viện có sẵn tên prefix.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="2" t="n">
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>05-ctdt-khong-phankhoa.xlsx</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>CTĐT không phân Khoa (mẫu Bộ)</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Ban Sau Đại học</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>CTDT</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Tham khảo</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Dữ liệu CTĐT đã có đầy đủ trong file 04.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>06-hocvien-ncs-sdh.xlsx</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Học viên Cao học &amp; NCS (~9.600 dòng)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Ban Sau Đại học</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>HT_NCS</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Quy mô SĐH</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Dùng</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Đếm 'Đang học' theo mã ngành (7 ký tự đầu); leading 8 = ThS, 9 = TS.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="2" t="n">
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>07-quymo-nhansu-gv.xlsx</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Danh sách nhân sự — quy mô GV (1.070 dòng)</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Ban Phát triển Tổ chức - Nhân lực</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Danhsach</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Quy mô giảng viên</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Dùng</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Lọc Chức danh chứa 'Giảng viên' hoặc 'isb'. NCS toàn thời gian giữ lại (Nhóm 5).</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>08-donvi-giangday.xlsx</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Mã quản lý → Đơn vị giảng dạy (949 mapping)</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Ban Phát triển Tổ chức - Nhân lực</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Sheet1</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Đơn vị giảng dạy</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Dùng</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Mapping GV Nhóm 4.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -910,131 +932,131 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>File gộp đầu ra:</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Duthaokehoach_merged.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Sheet trong file gộp</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Nguồn</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Mô tả</t>
         </is>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Quy mô giảng viên</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>07-quymo-nhansu-gv.xlsx</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Danh sách 1.070 GV (22 cột chuẩn target).</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Phụ lục 2. DS môn học 2025</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>02 + 03</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>1.637 học phần kèm Đơn vị phụ trách &amp; cờ 'Tính định biên'.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Quy mô sinh viên</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>01-quymo-sinhvien-dh.xlsx</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>81 chương trình ĐH với quy mô SV phân theo hệ đào tạo.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Quy mô SĐH</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>06 + 04</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Ngành SĐH với quy mô ThS / NCS đang học, phân về Khoa.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Đơn vị giảng dạy</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>08-donvi-giangday.xlsx</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>949 ánh xạ Mã quản lý → Đơn vị giảng dạy.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Chuongtrinhdaotao</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>04-ctdt-co-phankhoa.xlsx</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>146 chương trình đào tạo (ĐH + ThS + TS).</t>
         </is>
@@ -1058,790 +1080,784 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="46" customWidth="1" min="5" max="5"/>
     <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>3.1. Mapping chi tiết từng file</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>File nguồn</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Cột nguồn</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Cột đích (file gộp)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Sheet đích</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Phép biến đổi</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="56" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="3" ht="56" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>01-quymo-sinhvien-dh.xlsx</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Tên chương trình đào tạo</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Tên chương trình đào tạo</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Quy mô sinh viên</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Sao chép trực tiếp</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Bỏ dòng cuối 'CỘNG'.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="56" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>01-quymo-sinhvien-dh.xlsx</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Khoa/Viện quản lý</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Khoa/Viện quản lý</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Quy mô sinh viên</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Chuẩn hoá về tên canonical</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Áp bảng tra prefix.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="5" ht="56" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>01-quymo-sinhvien-dh.xlsx</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>ISB-CQ, Chính quy, VB2 CQ, Liên thông CQ, VB1 VLVH, VB2 VLVH, Liên thông CĐ VLVH, Liên thông TC VLVH, CỘNG</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>9 cột số liệu sinh viên</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Quy mô sinh viên</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Parse số (mặc định 0)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5" ht="56" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>01-quymo-sinhvien-dh.xlsx</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>(suy luận)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>tong ĐHCQ, VLVH</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Quy mô sinh viên</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Σ 4 cột CQ-related ; Σ 4 cột VLVH-related</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>02-hocphan-sotiet-2025.xlsx</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Mã HP, Tên HP, Bậc đào tạo, Số LHP, Số tín chỉ, Tổng số tiết</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>6 cột tương ứng</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Phụ lục 2. DS môn học 2025</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Sao chép + parse số</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>03-monhoc-khoa-phutrach.xlsx</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Khoa (lookup theo Mã HP)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Đơn vị phụ trách</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Phụ lục 2. DS môn học 2025</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Join với 02 trên Mã HP</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>03 đã có tên canonical sẵn.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>(suy luận)</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>(không có)</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Phụ lục 2. DS môn học 2025</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Tự gắn 'Tính định biên' nếu đơn vị là Khoa/Viện/Trung tâm/Phòng dạy học</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Trừ admin (Ban GH, Văn phòng, Phòng Chăm sóc).</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>04-ctdt-co-phankhoa.xlsx</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Stt, Mã CT, Tên CT, Mã ngành, Tên ngành, Lĩnh vực, Trường thành viên, Khoa/Viện, Năm tuyển sinh, Trình độ, Loại hình, Hình thức đào tạo</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>13 cột tương ứng</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Chuongtrinhdaotao</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Sao chép; Khoa/Viện chuẩn hoá về canonical</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Layout giữ 1 cột trống D giữa 'Tên CT' và 'Mã ngành'.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11" ht="56" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>06-hocvien-ncs-sdh.xlsx</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Mã chương trình đào tạo (HT_NCS)</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Mã_Ngành_ThS, Mã_Ngành_TS</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Quy mô SĐH</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Lấy 7 ký tự đầu. Leading 8 = ThS, 9 = TS.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Ví dụ 834012137VI03 → 8340121 (ThS).</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>06-hocvien-ncs-sdh.xlsx</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Trạng thái học</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>(bộ lọc)</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Quy mô SĐH</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Chỉ giữ 'Đang học'</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12" ht="56" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>06-hocvien-ncs-sdh.xlsx</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>(count)</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Quy_mô_ThS, Quy_mô_TS</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Quy mô SĐH</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Đếm số học viên đang học theo (mã ngành × trình độ)</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Ghép Tên ngành &amp; Đơn vị từ 04.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>07-quymo-nhansu-gv.xlsx</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>22 cột chuẩn (Mã quản lý, Họ tên, …, Tình trạng làm việc)</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>22 cột tương ứng</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Quy mô giảng viên</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Parse số (Mã quản lý, CMND, Năm TN, ĐT); parse ngày (Ngày sinh); parse bool (Giới tính)</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Mã quản lý bỏ đuôi '.0' để join ổn định với 08.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15" ht="56" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>08-donvi-giangday.xlsx</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>(bỏ)</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Đơn vị giảng dạy</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Không xuất</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15" ht="56" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>08-donvi-giangday.xlsx</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Mã quản lý</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Mã quản lý</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Đơn vị giảng dạy</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Parse int</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Khoá join với 07.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>08-donvi-giangday.xlsx</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Đơn vị giảng dạy</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Đơn vị giảng dạy</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Đơn vị giảng dạy</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Sao chép trực tiếp</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>3.2. Bảng tra tên đơn vị (canonical map)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Tên không prefix (lowercase)</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Tên canonical (có prefix mã trường)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>khoa công nghệ thông tin kinh doanh</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>CNTK - Khoa Công nghệ thông tin kinh doanh</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>khoa thiết kế truyền thông</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>CNTK - Khoa Thiết kế Truyền thông</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>viện công nghệ thông minh và tương tác</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>CNTK - Viện Công nghệ thông minh và tương tác</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>viện đô thị thông minh và quản lý</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>CNTK - Viện Đô thị thông minh và quản lý</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>viện đổi mới sáng tạo</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>CNTK - Viện Đổi mới sáng tạo</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>khoa du lịch</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>KD - Khoa Du lịch</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>khoa kinh doanh quốc tế - marketing</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>KD - Khoa Kinh doanh quốc tế - Marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>khoa kế toán</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>KD - Khoa Kế toán</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>khoa ngân hàng</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>KD - Khoa Ngân hàng</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>khoa quản trị</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>KD - Khoa Quản trị</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>khoa tài chính</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>KD - Khoa Tài chính</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>khoa kinh tế</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>KTLQLNN - Khoa Kinh tế</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>khoa luật</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>KTLQLNN - Khoa Luật</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>khoa ngoại ngữ</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>KTLQLNN - Khoa Ngoại ngữ</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>khoa quản lý nhà nước</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>KTLQLNN - Khoa Quản lý nhà nước</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>khoa toán - thống kê</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>KTLQLNN - Khoa Toán - Thống kê</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>khoa tài chính công</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>KTLQLNN - Khoa Tài chính công</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>viện tài chính bền vững</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>KTLQLNN - Viện Tài chính bền vững</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>khoa tài chính - ngân hàng</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>PHVL - Khoa Tài chính - Ngân hàng</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tên không prefix (lowercase)</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Tên canonical (có prefix mã trường)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>khoa công nghệ thông tin kinh doanh</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>CNTK - Khoa Công nghệ thông tin kinh doanh</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>khoa thiết kế truyền thông</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>CNTK - Khoa Thiết kế Truyền thông</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>viện công nghệ thông minh và tương tác</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>CNTK - Viện Công nghệ thông minh và tương tác</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>viện đô thị thông minh và quản lý</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>CNTK - Viện Đô thị thông minh và quản lý</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>viện đổi mới sáng tạo</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>CNTK - Viện Đổi mới sáng tạo</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>khoa du lịch</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>KD - Khoa Du lịch</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>khoa kinh doanh quốc tế - marketing</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>KD - Khoa Kinh doanh quốc tế - Marketing</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>khoa kế toán</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>KD - Khoa Kế toán</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>khoa ngân hàng</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>KD - Khoa Ngân hàng</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>khoa quản trị</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>KD - Khoa Quản trị</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>khoa tài chính</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>KD - Khoa Tài chính</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>khoa kinh tế</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>KTLQLNN - Khoa Kinh tế</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>khoa luật</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>KTLQLNN - Khoa Luật</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>khoa ngoại ngữ</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>KTLQLNN - Khoa Ngoại ngữ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>khoa quản lý nhà nước</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>KTLQLNN - Khoa Quản lý nhà nước</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>khoa toán - thống kê</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>KTLQLNN - Khoa Toán - Thống kê</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>khoa tài chính công</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>KTLQLNN - Khoa Tài chính công</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>viện tài chính bền vững</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>KTLQLNN - Viện Tài chính bền vững</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>khoa tài chính - ngân hàng</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>PHVL - Khoa Tài chính - Ngân hàng</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Bảng tra được dựng tự động bằng cách quét tên đơn vị có prefix 'XXXX - Khoa…' trong file 03 và 08. Pipeline áp lên mọi sheet để đồng nhất tên đơn vị.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A22:B22"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>